--- a/cycle1-sdg7/outputs/sdg7_cycle1.xlsx
+++ b/cycle1-sdg7/outputs/sdg7_cycle1.xlsx
@@ -9,8 +9,7 @@
   <sheets>
     <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Top20_Gap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Data_Dictionary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="QA" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="QA" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -90371,777 +90370,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="64" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Data dictionary and sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>1. What is in this workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Tab</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Grain (one row is...)</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>Rows</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>What it is for</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>one country-year</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>2279</v>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>The full cleaned table. Formatted as an Excel Table named SDG7Data -- click inside it and Insert &gt; PivotTable to analyse it interactively.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Top20_Gap</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>one country</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>The widest gaps and the fastest-widening gaps, kept as two separate blocks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Data_Dictionary</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>one column or source</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>This tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>one check</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>Live formulas that re-verify the figures against the Data tab whenever the file opens.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>2. Indicators (the four UN SDG 7 series used)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Series code</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>SDG indicator</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>Official name</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>EG_ACS_ELEC</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>7.1.1</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>Proportion of population with access to electricity, by urban/rural</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>% of population</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>EG_EGY_CLEAN</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>7.1.2</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>Proportion of population with primary reliance on clean fuels and technology</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>% of population</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>EG_FEC_RNEW</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>7.2.1</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>Renewable energy share in the total final energy consumption</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>% of final consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>EG_EGY_PRIM</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>7.3.1</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>Energy intensity level of primary energy</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>MJ per constant 2021 PPP GDP</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>3. Provenance</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Series code</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>Custodian / data provider</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>Retrieved</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="inlineStr">
-        <is>
-          <t>Endpoint</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>EG_ACS_ELEC</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>World Bank (via UN Statistics Division SDG database)</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>https://unstats.un.org/sdgs/UNSDGAPIV5/v1/sdg/Series/Data?seriesCode=EG_ACS_ELEC</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>EG_EGY_CLEAN</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>Global Health Observatory (GHO), World Health Organization (WHO)</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>https://unstats.un.org/sdgs/UNSDGAPIV5/v1/sdg/Series/Data?seriesCode=EG_EGY_CLEAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>EG_FEC_RNEW</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>UN Statistics Division Energy Balances (2025); IEA (2025) World Energy Balances</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>https://unstats.un.org/sdgs/UNSDGAPIV5/v1/sdg/Series/Data?seriesCode=EG_FEC_RNEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>EG_EGY_PRIM</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>UN Statistics Division Energy Balances (2025); IEA (2025) World Energy Balances</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>https://unstats.un.org/sdgs/UNSDGAPIV5/v1/sdg/Series/Data?seriesCode=EG_EGY_PRIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>4. Columns</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>Reported or computed?</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>M49 code</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>UN M49 numeric country code. The API publishes no ISO code, so this is the only machine identifier available.</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>code</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Reported</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>UN long-form area name, unmodified. Some differ from everyday usage ("Lao People's Democratic Republic") and need aliasing in Tableau.</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Reported</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>SDG region</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>One of the 7 UN SDG regions, assigned from the API's GeoArea/Tree.</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Computed (02_clean_transform.py)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>Electricity access (%)</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>Share of population with access to electricity, all areas.</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>% of population</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Reported (7.1.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Clean cooking (%)</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>Share of population relying primarily on clean fuels and technology for cooking, all areas. WHO rounds these to whole numbers.</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>% of population</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Reported (7.1.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Energy intensity (MJ/$ PPP)</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>Primary energy per unit of GDP. Lower is more efficient.</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>MJ / constant 2021 PPP $</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Reported (7.3.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>Renewable share (%)</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>Renewables as a share of total final energy consumption.</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>% of final consumption</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Reported (7.2.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>Cooking gap (pp)</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>Electricity access minus clean cooking access. Positive means electricity is ahead. This is the project's signature metric.</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>percentage points</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Computed (in-cell formula)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>Electricity urban-rural gap (pp)</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>Urban electricity access minus rural, same country-year.</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>percentage points</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Computed (03_derive_metrics.py)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>Clean cooking urban-rural gap (pp)</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>Urban clean cooking access minus rural, same country-year.</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>percentage points</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>Computed (03_derive_metrics.py)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Change 2015-2024 (pp)</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>The 2024 value minus the 2015 value. A NEGATIVE change in a gap column means the gap narrowed, which is an improvement.</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>percentage points</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Computed (in-cell formula)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>5. Limitations (carried onto the Data Sources slide)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>Limitation</t>
-        </is>
-      </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="42" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>7.2.1 is sparse after 2022</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>The renewable-share series thins out badly in recent years -- only 129 areas report a 2024 value. It is kept in the workbook for context but no trend claim rests on it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="42" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>Clean cooking figures are modelled</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>WHO publishes 7.1.2 as a modelled estimate with uncertainty bounds, not a measurement. Afghanistan's 2024 all-areas value of 30% carries a range of 15-48%. The bounds are in sdg7_tidy.csv; they are deliberately not shown in the charts, which would be unreadable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="42" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>Electricity has no uncertainty bounds</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>Only the WHO series publishes them, so the two indicators are not equally precise even though they are plotted on the same axis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="42" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>Three year-on-year jumps exceed 20 pp</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>Afghanistan 2015-16 (+26.2 pp), Papua New Guinea 2023-24 (+22.8 pp) and Cambodia 2016-17 (+20.3 pp) in electricity access. These are revisions in the source data, not cleaning errors -- see the QA tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="42" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>34 countries have no cooking gap at all</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>Small territories (Aruba, Bermuda, Hong Kong, American Samoa and similar) appear in the electricity series but not in clean cooking, so no gap can be computed. They are kept in the Data tab with blank cells rather than dropped, so the absence is visible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>Five areas drop out entirely</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>French Guiana, Guadeloupe, Martinique, Mayotte and Reunion have no usable values; they are reported within France.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="42" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>Kosovo has no 2024 row</t>
-        </is>
-      </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>227 of the 228 countries carry a 2024 observation. Kosovo's series ends in 2023.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="42" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>Regional figures cannot be rebuilt from the Data tab</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>They are population-weighted aggregates published by the UN. Averaging the countries on the Data tab gives a different -- and wrong -- answer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="42" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>The 2030 projection is a pace check, not a forecast</t>
-        </is>
-      </c>
-      <c r="B48" s="17" t="inlineStr">
-        <is>
-          <t>Where it appears, it extrapolates the fitted 2015-2024 straight line. Access curves flatten near 100%, so it flatters slow movers, and countries with no measurable trend are excluded rather than assigned an arrival date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>Generated by scripts/04_build_excel.py on 2026-10-12 from data/processed/. Do not edit cells by hand -- re-run the script instead.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/cycle1-sdg7/outputs/sdg7_cycle1.xlsx
+++ b/cycle1-sdg7/outputs/sdg7_cycle1.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Top20_Gap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="QA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Data_Dictionary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="QA" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -90370,6 +90371,777 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Data dictionary and sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>1. What is in this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Grain (one row is...)</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>What it is for</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>one country-year</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>2279</v>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>The full cleaned table. Formatted as an Excel Table named SDG7Data -- click inside it and Insert &gt; PivotTable to analyse it interactively.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Top20_Gap</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>one country</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>The widest gaps and the fastest-widening gaps, kept as two separate blocks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Data_Dictionary</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>one column or source</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>This tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>one check</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Live formulas that re-verify the figures against the Data tab whenever the file opens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>2. Indicators (the four UN SDG 7 series used)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Series code</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>SDG indicator</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Official name</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>EG_ACS_ELEC</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>Proportion of population with access to electricity, by urban/rural</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>% of population</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>EG_EGY_CLEAN</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>7.1.2</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Proportion of population with primary reliance on clean fuels and technology</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>% of population</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>EG_FEC_RNEW</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>7.2.1</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Renewable energy share in the total final energy consumption</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>% of final consumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>EG_EGY_PRIM</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>7.3.1</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Energy intensity level of primary energy</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>MJ per constant 2021 PPP GDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>3. Provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Series code</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>Custodian / data provider</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>Retrieved</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>Endpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>EG_ACS_ELEC</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>World Bank (via UN Statistics Division SDG database)</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>https://unstats.un.org/sdgs/UNSDGAPIV5/v1/sdg/Series/Data?seriesCode=EG_ACS_ELEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>EG_EGY_CLEAN</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Global Health Observatory (GHO), World Health Organization (WHO)</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>https://unstats.un.org/sdgs/UNSDGAPIV5/v1/sdg/Series/Data?seriesCode=EG_EGY_CLEAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>EG_FEC_RNEW</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>UN Statistics Division Energy Balances (2025); IEA (2025) World Energy Balances</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>https://unstats.un.org/sdgs/UNSDGAPIV5/v1/sdg/Series/Data?seriesCode=EG_FEC_RNEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>EG_EGY_PRIM</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>UN Statistics Division Energy Balances (2025); IEA (2025) World Energy Balances</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>https://unstats.un.org/sdgs/UNSDGAPIV5/v1/sdg/Series/Data?seriesCode=EG_EGY_PRIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>4. Columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>Reported or computed?</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>M49 code</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>UN M49 numeric country code. The API publishes no ISO code, so this is the only machine identifier available.</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>UN long-form area name, unmodified. Some differ from everyday usage ("Lao People's Democratic Republic") and need aliasing in Tableau.</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>SDG region</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>One of the 7 UN SDG regions, assigned from the API's GeoArea/Tree.</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Computed (02_clean_transform.py)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Electricity access (%)</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Share of population with access to electricity, all areas.</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>% of population</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Reported (7.1.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Clean cooking (%)</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>Share of population relying primarily on clean fuels and technology for cooking, all areas. WHO rounds these to whole numbers.</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>% of population</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Reported (7.1.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Energy intensity (MJ/$ PPP)</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Primary energy per unit of GDP. Lower is more efficient.</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>MJ / constant 2021 PPP $</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Reported (7.3.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Renewable share (%)</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>Renewables as a share of total final energy consumption.</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>% of final consumption</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Reported (7.2.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Cooking gap (pp)</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>Electricity access minus clean cooking access. Positive means electricity is ahead. This is the project's signature metric.</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>percentage points</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Computed (in-cell formula)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Electricity urban-rural gap (pp)</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>Urban electricity access minus rural, same country-year.</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>percentage points</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Computed (03_derive_metrics.py)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Clean cooking urban-rural gap (pp)</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>Urban clean cooking access minus rural, same country-year.</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>percentage points</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Computed (03_derive_metrics.py)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Change 2015-2024 (pp)</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>The 2024 value minus the 2015 value. A NEGATIVE change in a gap column means the gap narrowed, which is an improvement.</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>percentage points</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Computed (in-cell formula)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>5. Limitations (carried onto the Data Sources slide)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Limitation</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>7.2.1 is sparse after 2022</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>The renewable-share series thins out badly in recent years -- only 129 areas report a 2024 value. It is kept in the workbook for context but no trend claim rests on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Clean cooking figures are modelled</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>WHO publishes 7.1.2 as a modelled estimate with uncertainty bounds, not a measurement. Afghanistan's 2024 all-areas value of 30% carries a range of 15-48%. The bounds are in sdg7_tidy.csv; they are deliberately not shown in the charts, which would be unreadable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Electricity has no uncertainty bounds</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>Only the WHO series publishes them, so the two indicators are not equally precise even though they are plotted on the same axis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Three year-on-year jumps exceed 20 pp</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>Afghanistan 2015-16 (+26.2 pp), Papua New Guinea 2023-24 (+22.8 pp) and Cambodia 2016-17 (+20.3 pp) in electricity access. These are revisions in the source data, not cleaning errors -- see the QA tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>34 countries have no cooking gap at all</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>Small territories (Aruba, Bermuda, Hong Kong, American Samoa and similar) appear in the electricity series but not in clean cooking, so no gap can be computed. They are kept in the Data tab with blank cells rather than dropped, so the absence is visible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Five areas drop out entirely</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>French Guiana, Guadeloupe, Martinique, Mayotte and Reunion have no usable values; they are reported within France.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Kosovo has no 2024 row</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>227 of the 228 countries carry a 2024 observation. Kosovo's series ends in 2023.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Regional figures cannot be rebuilt from the Data tab</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>They are population-weighted aggregates published by the UN. Averaging the countries on the Data tab gives a different -- and wrong -- answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>The 2030 projection is a pace check, not a forecast</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>Where it appears, it extrapolates the fitted 2015-2024 straight line. Access curves flatten near 100%, so it flatters slow movers, and countries with no measurable trend are excluded rather than assigned an arrival date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>Generated by scripts/04_build_excel.py on 2026-10-12 from data/processed/. Do not edit cells by hand -- re-run the script instead.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
